--- a/game32/web.xlsx
+++ b/game32/web.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>domain</t>
   </si>
@@ -47,7 +47,55 @@
     <t>json</t>
   </si>
   <si>
-    <t>desertwoodrat.com</t>
+    <t>play.moosenose.site</t>
+  </si>
+  <si>
+    <t>#ffc408</t>
+  </si>
+  <si>
+    <t>#ba8677</t>
+  </si>
+  <si>
+    <t>sec.moosenose.site</t>
+  </si>
+  <si>
+    <t>#ebd86c</t>
+  </si>
+  <si>
+    <t>#2e56a3</t>
+  </si>
+  <si>
+    <t>sec.eunoias.cloud</t>
+  </si>
+  <si>
+    <t>#f0ff31</t>
+  </si>
+  <si>
+    <t>sec.uminous.top</t>
+  </si>
+  <si>
+    <t>#27456c</t>
+  </si>
+  <si>
+    <t>sec.nebulous.top</t>
+  </si>
+  <si>
+    <t>#98b0ca</t>
+  </si>
+  <si>
+    <t>fathom-hold.com</t>
+  </si>
+  <si>
+    <t>solace-rift.com</t>
+  </si>
+  <si>
+    <t>#f597ba</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>deasils.com</t>
   </si>
   <si>
     <t>#f7ece7</t>
@@ -56,7 +104,7 @@
     <t>#a61b29</t>
   </si>
   <si>
-    <t>desertskink.com</t>
+    <t>cacodox.com</t>
   </si>
   <si>
     <t>#e2e1dd</t>
@@ -65,7 +113,7 @@
     <t>#8abe98</t>
   </si>
   <si>
-    <t>seamisty.com</t>
+    <t>gloamis.com</t>
   </si>
   <si>
     <t>#fafbe6</t>
@@ -74,7 +122,7 @@
     <t>#a48ce6</t>
   </si>
   <si>
-    <t>seareefy.com</t>
+    <t>inglenok.com</t>
   </si>
   <si>
     <t>#c6e6e8</t>
@@ -83,58 +131,13 @@
     <t>#373834</t>
   </si>
   <si>
-    <t>seascenic.com</t>
+    <t>jentacul.com</t>
   </si>
   <si>
     <t>#e3e3e5</t>
   </si>
   <si>
     <t>#707899</t>
-  </si>
-  <si>
-    <t>sec.eunoias.cloud</t>
-  </si>
-  <si>
-    <t>#f0ff31</t>
-  </si>
-  <si>
-    <t>sec.uminous.top</t>
-  </si>
-  <si>
-    <t>#27456c</t>
-  </si>
-  <si>
-    <t>sec.nebulous.top</t>
-  </si>
-  <si>
-    <t>#98b0ca</t>
-  </si>
-  <si>
-    <t>fathom-hold.com</t>
-  </si>
-  <si>
-    <t>solace-rift.com</t>
-  </si>
-  <si>
-    <t>#f597ba</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>deasils.com</t>
-  </si>
-  <si>
-    <t>cacodox.com</t>
-  </si>
-  <si>
-    <t>gloamis.com</t>
-  </si>
-  <si>
-    <t>inglenok.com</t>
-  </si>
-  <si>
-    <t>jentacul.com</t>
   </si>
   <si>
     <t>spuddles.fun</t>
@@ -381,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="49">
+  <fills count="53">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,6 +484,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF98B0CA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC408"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA8677"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBD86C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E56A3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -810,7 +837,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -834,16 +861,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -852,25 +879,13 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -933,8 +948,20 @@
     <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1006,38 +1033,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1459,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1480,64 +1489,27 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="24">
-        <v>3</v>
-      </c>
-      <c r="E4" s="24">
-        <v>2</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="24">
-        <v>4</v>
-      </c>
-      <c r="E5" s="24">
-        <v>2</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="24">
-        <v>5</v>
-      </c>
-      <c r="E6" s="24">
-        <v>2</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="desertwoodrat.com"/>
-    <hyperlink ref="A3" r:id="rId2" display="desertskink.com"/>
-    <hyperlink ref="A4" r:id="rId3" display="seamisty.com"/>
-    <hyperlink ref="A5" r:id="rId4" display="seareefy.com"/>
-    <hyperlink ref="A6" r:id="rId5" display="seascenic.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1571,10 +1543,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1585,10 +1557,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="19" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1599,10 +1571,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4">
@@ -1669,19 +1641,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5"/>
     </row>
@@ -1731,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1739,73 +1711,73 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:7">
       <c r="A5" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" s="13" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
